--- a/data/trans_orig/P5711-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P5711-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir ayuda cuando se está enfermo en la cama en 2007</t>
+          <t>Población según la frecuencia de recibir ayuda cuando se está enfermo en la cama en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>618532</t>
+          <t>614723</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>678144</t>
+          <t>675469</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>701628</t>
+          <t>698472</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>772579</t>
+          <t>767340</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1330820</t>
+          <t>1338442</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1431383</t>
+          <t>1432425</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>61,04%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>199271</t>
+          <t>201492</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>253058</t>
+          <t>255164</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>259579</t>
+          <t>255005</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>317568</t>
+          <t>317977</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>473028</t>
+          <t>470554</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>556311</t>
+          <t>554463</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,63%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>90062</t>
+          <t>89830</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>127650</t>
+          <t>129870</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>141550</t>
+          <t>143679</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>189147</t>
+          <t>190826</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>241562</t>
+          <t>246359</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>302587</t>
+          <t>305586</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29985</t>
+          <t>30114</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54296</t>
+          <t>55259</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85544</t>
+          <t>84821</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>124938</t>
+          <t>124147</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>121655</t>
+          <t>122762</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>168311</t>
+          <t>170043</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>3919</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17803</t>
+          <t>18629</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15357</t>
+          <t>16122</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35301</t>
+          <t>34662</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23027</t>
+          <t>23064</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>47395</t>
+          <t>46145</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1225450</t>
+          <t>1222858</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1299866</t>
+          <t>1297058</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>998068</t>
+          <t>995562</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1069909</t>
+          <t>1075721</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2242951</t>
+          <t>2243212</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2347633</t>
+          <t>2347778</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>272402</t>
+          <t>269224</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>338616</t>
+          <t>334233</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>329313</t>
+          <t>326663</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>395273</t>
+          <t>393778</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>615147</t>
+          <t>619978</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>712066</t>
+          <t>706817</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>76446</t>
+          <t>75963</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>115895</t>
+          <t>113520</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>105072</t>
+          <t>105618</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>148991</t>
+          <t>148270</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>194402</t>
+          <t>193498</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>251859</t>
+          <t>250138</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16912</t>
+          <t>16855</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37192</t>
+          <t>37577</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40869</t>
+          <t>41650</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71299</t>
+          <t>71642</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62331</t>
+          <t>64652</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>98682</t>
+          <t>100547</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4066</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17912</t>
+          <t>17495</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6603</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21777</t>
+          <t>21906</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>13095</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32927</t>
+          <t>33442</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>367622</t>
+          <t>365141</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>412523</t>
+          <t>410690</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>304218</t>
+          <t>306741</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>346597</t>
+          <t>347350</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>687556</t>
+          <t>686999</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>746502</t>
+          <t>750265</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>73,07%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>94672</t>
+          <t>96106</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>132990</t>
+          <t>134712</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>85331</t>
+          <t>85268</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>122971</t>
+          <t>119930</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>190299</t>
+          <t>188477</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>241856</t>
+          <t>243024</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,67%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23142</t>
+          <t>21646</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>47421</t>
+          <t>45097</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19989</t>
+          <t>20279</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40752</t>
+          <t>41964</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>47987</t>
+          <t>47865</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>80104</t>
+          <t>79324</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6812</t>
+          <t>7693</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23644</t>
+          <t>24780</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7171</t>
+          <t>7025</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23142</t>
+          <t>22086</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17427</t>
+          <t>17311</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40129</t>
+          <t>40387</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11756</t>
+          <t>11417</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11117</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2242880</t>
+          <t>2243506</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2348830</t>
+          <t>2350593</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2035771</t>
+          <t>2042485</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2152681</t>
+          <t>2153914</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4320224</t>
+          <t>4314785</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4480472</t>
+          <t>4471263</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,19%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>596519</t>
+          <t>598204</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>689805</t>
+          <t>690294</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>702449</t>
+          <t>697462</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>800660</t>
+          <t>794675</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1328839</t>
+          <t>1326863</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1457283</t>
+          <t>1463458</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>208609</t>
+          <t>206025</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>266064</t>
+          <t>266017</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>289324</t>
+          <t>288990</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>357349</t>
+          <t>355428</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>509560</t>
+          <t>508775</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>601020</t>
+          <t>599422</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>63387</t>
+          <t>62771</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>101753</t>
+          <t>100777</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>146670</t>
+          <t>146346</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>198190</t>
+          <t>199198</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>218695</t>
+          <t>218446</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>283495</t>
+          <t>284170</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9926</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>29732</t>
+          <t>31065</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>29704</t>
+          <t>29896</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>57101</t>
+          <t>55463</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>45015</t>
+          <t>43895</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>76898</t>
+          <t>76747</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir ayuda cuando se está enfermo en la cama en 2012</t>
+          <t>Población según la frecuencia de recibir ayuda cuando se está enfermo en la cama en 2012 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>663833</t>
+          <t>664142</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>720607</t>
+          <t>722748</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>847429</t>
+          <t>849843</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>918941</t>
+          <t>921347</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1529548</t>
+          <t>1536395</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1621776</t>
+          <t>1624280</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,49%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>165809</t>
+          <t>167313</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>218386</t>
+          <t>218057</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>277946</t>
+          <t>275050</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>340489</t>
+          <t>338365</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>459031</t>
+          <t>461852</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>543071</t>
+          <t>539305</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,4%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49008</t>
+          <t>52044</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>80916</t>
+          <t>84442</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74558</t>
+          <t>72114</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>112393</t>
+          <t>109131</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>132472</t>
+          <t>132634</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>184051</t>
+          <t>182922</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8960</t>
+          <t>9238</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24477</t>
+          <t>25334</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22004</t>
+          <t>21646</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45378</t>
+          <t>45250</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35627</t>
+          <t>35735</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65504</t>
+          <t>64361</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11604</t>
+          <t>11042</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11304</t>
+          <t>11857</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28620</t>
+          <t>31207</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15897</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>35634</t>
+          <t>35762</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1370574</t>
+          <t>1365857</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1453177</t>
+          <t>1449952</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1105115</t>
+          <t>1102760</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1187141</t>
+          <t>1183626</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2496288</t>
+          <t>2497003</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2612078</t>
+          <t>2617646</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,4%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>365857</t>
+          <t>366292</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>437851</t>
+          <t>443206</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>389810</t>
+          <t>391385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>464220</t>
+          <t>463117</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>784092</t>
+          <t>776532</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>888778</t>
+          <t>879207</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>95893</t>
+          <t>98361</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>140205</t>
+          <t>144045</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>110843</t>
+          <t>109443</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>157351</t>
+          <t>156910</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>218149</t>
+          <t>220188</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>282950</t>
+          <t>283049</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15614</t>
+          <t>15131</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36504</t>
+          <t>35687</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27649</t>
+          <t>29353</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54436</t>
+          <t>55582</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49310</t>
+          <t>50368</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82907</t>
+          <t>84154</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>3692</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14302</t>
+          <t>14826</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21121</t>
+          <t>21167</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11245</t>
+          <t>11357</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30739</t>
+          <t>29670</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>335935</t>
+          <t>335465</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>380089</t>
+          <t>378704</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>322052</t>
+          <t>320661</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>362304</t>
+          <t>362238</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>675345</t>
+          <t>672922</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>731716</t>
+          <t>731203</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,06%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>65238</t>
+          <t>67454</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>102731</t>
+          <t>104396</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76924</t>
+          <t>76793</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>112983</t>
+          <t>114984</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>149663</t>
+          <t>153576</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>200799</t>
+          <t>204974</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19447</t>
+          <t>19313</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45648</t>
+          <t>44233</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8290</t>
+          <t>8604</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26658</t>
+          <t>26201</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>31340</t>
+          <t>32162</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>63465</t>
+          <t>61118</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>940</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8560</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13106</t>
+          <t>13267</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16972</t>
+          <t>17311</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11668</t>
+          <t>11469</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,62 +5543,62 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>3397</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>14254</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>3397</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>13274</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2407689</t>
+          <t>2414796</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2513543</t>
+          <t>2527112</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2311717</t>
+          <t>2316240</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2430116</t>
+          <t>2432689</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4764598</t>
+          <t>4751444</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4923473</t>
+          <t>4915934</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,64%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>629655</t>
+          <t>625701</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>728382</t>
+          <t>721415</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>779992</t>
+          <t>772460</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>885933</t>
+          <t>878483</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1429796</t>
+          <t>1435016</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1570233</t>
+          <t>1582519</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>183099</t>
+          <t>184808</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>243023</t>
+          <t>243085</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>207224</t>
+          <t>210795</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>273122</t>
+          <t>272333</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>408385</t>
+          <t>410357</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>493558</t>
+          <t>498789</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29330</t>
+          <t>30348</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56458</t>
+          <t>57207</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>60318</t>
+          <t>61363</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>97195</t>
+          <t>100166</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>100283</t>
+          <t>101035</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>144211</t>
+          <t>145254</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8896</t>
+          <t>8754</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26743</t>
+          <t>25772</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19894</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>43314</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>33911</t>
+          <t>33749</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>62035</t>
+          <t>62516</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir ayuda cuando se está enfermo en la cama en 2016</t>
+          <t>Población según la frecuencia de recibir ayuda cuando se está enfermo en la cama en 2016 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>384669</t>
+          <t>383907</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>436849</t>
+          <t>435549</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>469695</t>
+          <t>466102</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>535246</t>
+          <t>534468</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>864544</t>
+          <t>871954</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>949674</t>
+          <t>958055</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,84%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>228647</t>
+          <t>229418</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>278566</t>
+          <t>280277</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>290468</t>
+          <t>292154</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>353742</t>
+          <t>355472</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>538025</t>
+          <t>535062</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>621585</t>
+          <t>616425</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,29%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56236</t>
+          <t>57475</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>89869</t>
+          <t>89101</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>102979</t>
+          <t>104151</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>149596</t>
+          <t>146125</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>170671</t>
+          <t>168415</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>223146</t>
+          <t>223803</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7342</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23982</t>
+          <t>22840</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26794</t>
+          <t>26249</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51633</t>
+          <t>51694</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37835</t>
+          <t>36799</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66199</t>
+          <t>67059</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>6880</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>4188</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>17194</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5097</t>
+          <t>5620</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18650</t>
+          <t>19108</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1134157</t>
+          <t>1129440</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1223389</t>
+          <t>1219317</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>987318</t>
+          <t>984883</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1072316</t>
+          <t>1071720</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2144674</t>
+          <t>2143192</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2270790</t>
+          <t>2273445</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>56,03%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>618334</t>
+          <t>619991</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>704008</t>
+          <t>705624</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>664670</t>
+          <t>663168</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>751551</t>
+          <t>745356</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1307346</t>
+          <t>1307682</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1431583</t>
+          <t>1433072</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,32%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>160977</t>
+          <t>163522</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>216124</t>
+          <t>218244</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>174441</t>
+          <t>175860</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>230168</t>
+          <t>232153</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>352527</t>
+          <t>351137</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>427985</t>
+          <t>430552</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17726</t>
+          <t>17565</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41421</t>
+          <t>41006</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23238</t>
+          <t>23228</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46728</t>
+          <t>46722</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46318</t>
+          <t>44476</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>78278</t>
+          <t>77237</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9906</t>
+          <t>10383</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26377</t>
+          <t>26476</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>7044</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21427</t>
+          <t>22229</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21228</t>
+          <t>20562</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>41553</t>
+          <t>42800</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>316488</t>
+          <t>315082</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>362563</t>
+          <t>361530</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>323141</t>
+          <t>320505</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>367765</t>
+          <t>366591</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>651296</t>
+          <t>651191</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>718148</t>
+          <t>717191</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,54%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>152402</t>
+          <t>151240</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>196616</t>
+          <t>196310</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>127683</t>
+          <t>127853</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>169201</t>
+          <t>170827</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>289382</t>
+          <t>293286</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>353135</t>
+          <t>353322</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,29%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19860</t>
+          <t>19327</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43581</t>
+          <t>42854</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31647</t>
+          <t>31326</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>57977</t>
+          <t>57553</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>57741</t>
+          <t>56438</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>92925</t>
+          <t>90595</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8639</t>
+          <t>8603</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4189</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16884</t>
+          <t>17294</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>6836</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21200</t>
+          <t>21996</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -8467,97 +8467,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2413</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2092</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>8368</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>2413</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>7349</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>2413</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>8325</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1867639</t>
+          <t>1872595</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1989481</t>
+          <t>1982980</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1813260</t>
+          <t>1815593</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1932238</t>
+          <t>1938963</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3717306</t>
+          <t>3719166</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3883554</t>
+          <t>3884909</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,31%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1033750</t>
+          <t>1036162</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1148304</t>
+          <t>1144236</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1122237</t>
+          <t>1120475</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1235061</t>
+          <t>1234693</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2189597</t>
+          <t>2196990</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2346832</t>
+          <t>2356714</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,16%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>256992</t>
+          <t>257065</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>323160</t>
+          <t>324670</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>331979</t>
+          <t>330084</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>406026</t>
+          <t>404202</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>605845</t>
+          <t>607150</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>705349</t>
+          <t>705564</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>33114</t>
+          <t>33183</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>60810</t>
+          <t>61817</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>63749</t>
+          <t>63926</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>100664</t>
+          <t>100230</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>102462</t>
+          <t>106011</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>148142</t>
+          <t>150858</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11255</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>28106</t>
+          <t>29458</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15733</t>
+          <t>15731</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>35567</t>
+          <t>34887</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>30864</t>
+          <t>30545</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>57645</t>
+          <t>58543</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir ayuda cuando se está enfermo en la cama en 2023</t>
+          <t>Población según la frecuencia de recibir ayuda cuando se está enfermo en la cama en 2023 (tasa de respuesta: 99,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9610,12 +9610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>248818</t>
+          <t>246782</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>289775</t>
+          <t>290026</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>330969</t>
+          <t>333304</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>373955</t>
+          <t>375213</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>590719</t>
+          <t>594138</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>650330</t>
+          <t>651909</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,81%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120189</t>
+          <t>120024</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>156503</t>
+          <t>158653</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>204725</t>
+          <t>205495</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>242724</t>
+          <t>243603</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>336279</t>
+          <t>334659</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>388786</t>
+          <t>387535</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,8%</t>
         </is>
       </c>
     </row>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42247</t>
+          <t>41439</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67533</t>
+          <t>67163</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>81256</t>
+          <t>78323</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>106496</t>
+          <t>105682</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>131737</t>
+          <t>130786</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>167069</t>
+          <t>166227</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28735</t>
+          <t>28859</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48993</t>
+          <t>48692</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45403</t>
+          <t>46181</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66051</t>
+          <t>66480</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79786</t>
+          <t>78117</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>107992</t>
+          <t>107143</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9040</t>
+          <t>9121</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21456</t>
+          <t>21633</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13852</t>
+          <t>13808</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26586</t>
+          <t>26471</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25215</t>
+          <t>25612</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43525</t>
+          <t>42810</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1339491</t>
+          <t>1334219</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1722737</t>
+          <t>1716580</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>880553</t>
+          <t>880999</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1343354</t>
+          <t>1337973</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2312750</t>
+          <t>2282211</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2918812</t>
+          <t>2939218</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>65,09%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>408328</t>
+          <t>415802</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>694932</t>
+          <t>698470</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>453918</t>
+          <t>456805</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>711762</t>
+          <t>711337</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1001102</t>
+          <t>977867</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1378006</t>
+          <t>1373990</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,43%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>108755</t>
+          <t>102924</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>184242</t>
+          <t>186482</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>135275</t>
+          <t>135665</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>819785</t>
+          <t>862872</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>278998</t>
+          <t>283439</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1130587</t>
+          <t>1349675</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>29,89%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27593</t>
+          <t>29003</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58082</t>
+          <t>59669</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43319</t>
+          <t>45112</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77214</t>
+          <t>77601</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81855</t>
+          <t>80799</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>128893</t>
+          <t>126614</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14654</t>
+          <t>14882</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34500</t>
+          <t>34948</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12281</t>
+          <t>12608</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29985</t>
+          <t>29450</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32730</t>
+          <t>30974</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>60553</t>
+          <t>57774</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>398316</t>
+          <t>395841</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>452046</t>
+          <t>451481</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>440810</t>
+          <t>442836</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>483491</t>
+          <t>481103</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>854950</t>
+          <t>852063</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>922258</t>
+          <t>921060</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,8%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>143096</t>
+          <t>142148</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>187681</t>
+          <t>189675</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>140759</t>
+          <t>140348</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>179564</t>
+          <t>177526</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>293967</t>
+          <t>293914</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>353495</t>
+          <t>351872</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24197</t>
+          <t>25495</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>68451</t>
+          <t>72534</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14053</t>
+          <t>13211</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29328</t>
+          <t>28404</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>44218</t>
+          <t>44016</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>89058</t>
+          <t>96414</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18971</t>
+          <t>19029</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7962</t>
+          <t>7847</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19499</t>
+          <t>19022</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15298</t>
+          <t>15332</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32852</t>
+          <t>33094</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9279</t>
+          <t>9118</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8924</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4245</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14437</t>
+          <t>15298</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2029420</t>
+          <t>2034129</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2447132</t>
+          <t>2460446</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1652738</t>
+          <t>1685891</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2152454</t>
+          <t>2165836</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3829064</t>
+          <t>3802753</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4449626</t>
+          <t>4437798</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,73%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>690863</t>
+          <t>694924</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>997129</t>
+          <t>995598</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>820621</t>
+          <t>823263</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1092552</t>
+          <t>1093033</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1643358</t>
+          <t>1657947</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2054861</t>
+          <t>2059043</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>192153</t>
+          <t>189828</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>285555</t>
+          <t>285156</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>250112</t>
+          <t>246995</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1028442</t>
+          <t>961276</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>484751</t>
+          <t>483559</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1396043</t>
+          <t>1386250</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,59%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>68824</t>
+          <t>71133</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>110528</t>
+          <t>111763</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>106115</t>
+          <t>105480</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>149683</t>
+          <t>150856</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>187777</t>
+          <t>184348</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>250632</t>
+          <t>248007</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>30672</t>
+          <t>29791</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>54580</t>
+          <t>54712</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>32885</t>
+          <t>34100</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>56906</t>
+          <t>57116</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>69491</t>
+          <t>69946</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>104965</t>
+          <t>103344</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P5711-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P5711-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>614723</t>
+          <t>618212</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>675469</t>
+          <t>678528</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>698472</t>
+          <t>698861</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>767340</t>
+          <t>769315</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1338442</t>
+          <t>1339424</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1432425</t>
+          <t>1431173</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>60,98%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>201492</t>
+          <t>196725</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>255164</t>
+          <t>250724</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>255005</t>
+          <t>257490</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>317977</t>
+          <t>315451</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>470554</t>
+          <t>472134</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>554463</t>
+          <t>552396</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89830</t>
+          <t>89276</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>129870</t>
+          <t>127306</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>143679</t>
+          <t>142624</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>190826</t>
+          <t>191627</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>246359</t>
+          <t>245311</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>305586</t>
+          <t>305655</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30114</t>
+          <t>29396</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55259</t>
+          <t>55149</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>84821</t>
+          <t>86006</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>124147</t>
+          <t>125396</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>122762</t>
+          <t>121758</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>170043</t>
+          <t>169441</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3919</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18629</t>
+          <t>17995</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16122</t>
+          <t>15323</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>34662</t>
+          <t>35128</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23064</t>
+          <t>23758</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46145</t>
+          <t>47703</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1222858</t>
+          <t>1227919</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1297058</t>
+          <t>1301281</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>995562</t>
+          <t>992978</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1075721</t>
+          <t>1072225</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2243212</t>
+          <t>2238299</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2347778</t>
+          <t>2346796</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,52%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>269224</t>
+          <t>272128</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>334233</t>
+          <t>333530</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>326663</t>
+          <t>327846</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>393778</t>
+          <t>396434</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>619978</t>
+          <t>622141</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>706817</t>
+          <t>712358</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>75963</t>
+          <t>76096</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>113520</t>
+          <t>114316</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>105618</t>
+          <t>104634</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>148270</t>
+          <t>147537</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>193498</t>
+          <t>194558</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>250138</t>
+          <t>250110</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16855</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37577</t>
+          <t>37784</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41650</t>
+          <t>40036</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71642</t>
+          <t>70656</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>64652</t>
+          <t>62751</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100547</t>
+          <t>101422</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>4386</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17495</t>
+          <t>17387</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21906</t>
+          <t>22282</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,47 +1917,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>21373</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>13320</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>33760</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>21373</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>13095</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>33442</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>365141</t>
+          <t>366911</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>410690</t>
+          <t>409827</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>306741</t>
+          <t>306899</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>347350</t>
+          <t>348626</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>686999</t>
+          <t>685300</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>750265</t>
+          <t>747977</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>72,85%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>96106</t>
+          <t>96396</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134712</t>
+          <t>136037</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>85268</t>
+          <t>85076</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>119930</t>
+          <t>121446</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>188477</t>
+          <t>190110</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>243024</t>
+          <t>244514</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21646</t>
+          <t>22151</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45097</t>
+          <t>45757</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20279</t>
+          <t>19608</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41964</t>
+          <t>42549</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>47865</t>
+          <t>49129</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>79324</t>
+          <t>80900</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7693</t>
+          <t>6919</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24780</t>
+          <t>23244</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7025</t>
+          <t>6405</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22086</t>
+          <t>21941</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17311</t>
+          <t>17544</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40387</t>
+          <t>39877</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11417</t>
+          <t>11597</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11117</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2243506</t>
+          <t>2243389</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2350593</t>
+          <t>2350168</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2042485</t>
+          <t>2042091</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2153914</t>
+          <t>2149664</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4314785</t>
+          <t>4319479</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4471263</t>
+          <t>4478697</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,3%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>598204</t>
+          <t>597867</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>690294</t>
+          <t>691012</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>697462</t>
+          <t>702051</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>794675</t>
+          <t>800361</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1326863</t>
+          <t>1323102</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1463458</t>
+          <t>1451930</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,82%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>206025</t>
+          <t>204900</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>266017</t>
+          <t>265395</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>288990</t>
+          <t>286233</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>355428</t>
+          <t>353704</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>508775</t>
+          <t>514428</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>599422</t>
+          <t>604712</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>62771</t>
+          <t>63285</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>100777</t>
+          <t>101024</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>146346</t>
+          <t>145394</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>199198</t>
+          <t>198980</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>218446</t>
+          <t>220858</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>284170</t>
+          <t>285009</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10974</t>
+          <t>10453</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>31065</t>
+          <t>30507</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>29896</t>
+          <t>27865</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>55463</t>
+          <t>55028</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>43895</t>
+          <t>44855</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>76747</t>
+          <t>77321</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>664142</t>
+          <t>662705</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>722748</t>
+          <t>724751</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>849843</t>
+          <t>847709</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>921347</t>
+          <t>917572</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1536395</t>
+          <t>1534243</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1624280</t>
+          <t>1624216</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>167313</t>
+          <t>164253</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>218057</t>
+          <t>217740</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>275050</t>
+          <t>278260</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>338365</t>
+          <t>339035</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>461852</t>
+          <t>457491</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>539305</t>
+          <t>538975</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,39%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>52044</t>
+          <t>50417</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>84442</t>
+          <t>81313</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>72114</t>
+          <t>73744</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>109131</t>
+          <t>112020</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>132634</t>
+          <t>130040</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>182922</t>
+          <t>180220</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9238</t>
+          <t>9294</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25334</t>
+          <t>24486</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21646</t>
+          <t>22669</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45250</t>
+          <t>45454</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35735</t>
+          <t>34095</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64361</t>
+          <t>61794</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11042</t>
+          <t>11255</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11857</t>
+          <t>11275</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31207</t>
+          <t>29813</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15574</t>
+          <t>15670</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>35762</t>
+          <t>36244</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1365857</t>
+          <t>1365374</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1449952</t>
+          <t>1452224</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1102760</t>
+          <t>1101015</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1183626</t>
+          <t>1186161</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2497003</t>
+          <t>2498974</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2617646</t>
+          <t>2608266</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,14%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>366292</t>
+          <t>366394</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>443206</t>
+          <t>439484</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>391385</t>
+          <t>390671</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>463117</t>
+          <t>465584</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>776532</t>
+          <t>778386</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>879207</t>
+          <t>882401</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>98361</t>
+          <t>97055</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>144045</t>
+          <t>143599</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>109443</t>
+          <t>109683</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>156910</t>
+          <t>156207</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>220188</t>
+          <t>221063</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>283049</t>
+          <t>285557</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15131</t>
+          <t>15609</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35687</t>
+          <t>35974</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29353</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55582</t>
+          <t>54960</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50368</t>
+          <t>50467</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84154</t>
+          <t>80676</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14826</t>
+          <t>14193</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21167</t>
+          <t>21080</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11357</t>
+          <t>11405</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29670</t>
+          <t>29275</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>335465</t>
+          <t>335829</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>378704</t>
+          <t>379161</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>320661</t>
+          <t>324007</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>362238</t>
+          <t>361859</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>672922</t>
+          <t>672761</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>731203</t>
+          <t>730958</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,04%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>67454</t>
+          <t>67534</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>104396</t>
+          <t>102685</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76793</t>
+          <t>75490</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>114984</t>
+          <t>112944</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>153576</t>
+          <t>153108</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>204974</t>
+          <t>205744</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,97%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19313</t>
+          <t>19628</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>44233</t>
+          <t>44245</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8604</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26201</t>
+          <t>25621</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>32162</t>
+          <t>31238</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>61118</t>
+          <t>62292</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>933</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8989</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13267</t>
+          <t>13212</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>3784</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17311</t>
+          <t>15996</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11469</t>
+          <t>11230</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14254</t>
+          <t>11365</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2414796</t>
+          <t>2405695</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2527112</t>
+          <t>2516448</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2316240</t>
+          <t>2312001</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2432689</t>
+          <t>2427625</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4751444</t>
+          <t>4753086</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4915934</t>
+          <t>4914125</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,61%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>625701</t>
+          <t>631054</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>721415</t>
+          <t>721824</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>772460</t>
+          <t>776246</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>878483</t>
+          <t>879941</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1435016</t>
+          <t>1439287</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1582519</t>
+          <t>1578308</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>184808</t>
+          <t>183213</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>243085</t>
+          <t>243715</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>210795</t>
+          <t>209453</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>272333</t>
+          <t>275661</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>410357</t>
+          <t>409193</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>498789</t>
+          <t>494980</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30348</t>
+          <t>31367</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>57207</t>
+          <t>58768</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>61363</t>
+          <t>62634</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>100166</t>
+          <t>100377</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>101035</t>
+          <t>98300</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>145254</t>
+          <t>145497</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8754</t>
+          <t>9878</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25772</t>
+          <t>26506</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20329</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>43314</t>
+          <t>45328</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>33749</t>
+          <t>33759</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>62516</t>
+          <t>61868</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>383907</t>
+          <t>385381</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>435549</t>
+          <t>438678</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>466102</t>
+          <t>464219</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>534468</t>
+          <t>530708</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>871954</t>
+          <t>863908</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>958055</t>
+          <t>952520</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,53%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>229418</t>
+          <t>227722</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>280277</t>
+          <t>281334</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>292154</t>
+          <t>293895</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>355472</t>
+          <t>355787</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>535062</t>
+          <t>540548</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>616425</t>
+          <t>625129</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,79%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57475</t>
+          <t>57909</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>89101</t>
+          <t>89506</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>104151</t>
+          <t>104290</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>146125</t>
+          <t>147469</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>168415</t>
+          <t>169941</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>223803</t>
+          <t>225191</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22840</t>
+          <t>23091</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26249</t>
+          <t>25980</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51694</t>
+          <t>51215</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36799</t>
+          <t>39433</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67059</t>
+          <t>68601</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6880</t>
+          <t>6493</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4188</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17194</t>
+          <t>16387</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5620</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19108</t>
+          <t>18734</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1129440</t>
+          <t>1134464</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1219317</t>
+          <t>1224246</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>984883</t>
+          <t>986146</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1071720</t>
+          <t>1076533</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2143192</t>
+          <t>2148706</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2273445</t>
+          <t>2275551</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>56,08%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>619991</t>
+          <t>622153</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>705624</t>
+          <t>706924</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>663168</t>
+          <t>663410</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>745356</t>
+          <t>751615</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1307682</t>
+          <t>1302652</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1433072</t>
+          <t>1427907</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,19%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>163522</t>
+          <t>161022</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>218244</t>
+          <t>214475</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>175860</t>
+          <t>175812</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>232153</t>
+          <t>231317</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7614,7 +7614,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>351137</t>
+          <t>352202</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>430552</t>
+          <t>429381</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17565</t>
+          <t>17798</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41006</t>
+          <t>41782</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23228</t>
+          <t>23050</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46722</t>
+          <t>46823</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44476</t>
+          <t>46849</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77237</t>
+          <t>79733</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10383</t>
+          <t>9652</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26476</t>
+          <t>26453</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,82 +7800,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>13000</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>7128</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>23145</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>29590</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>20228</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>40535</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>0,5%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>13000</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>7044</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>22229</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>29590</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>20562</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>42800</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>315082</t>
+          <t>313842</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>361530</t>
+          <t>361031</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>320505</t>
+          <t>319661</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>366591</t>
+          <t>367554</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>651191</t>
+          <t>648105</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>717191</t>
+          <t>716584</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,49%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>151240</t>
+          <t>152022</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>196310</t>
+          <t>199660</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>127853</t>
+          <t>127177</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>170827</t>
+          <t>169095</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>293286</t>
+          <t>293993</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>353322</t>
+          <t>354862</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,43%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19327</t>
+          <t>19467</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>42854</t>
+          <t>43480</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31326</t>
+          <t>31705</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>57553</t>
+          <t>58151</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>56438</t>
+          <t>56569</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>90595</t>
+          <t>91379</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8603</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4336</t>
+          <t>4352</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17294</t>
+          <t>17346</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>6497</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21996</t>
+          <t>20532</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8368</t>
+          <t>7310</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7349</t>
+          <t>8348</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1872595</t>
+          <t>1867491</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1982980</t>
+          <t>1985999</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1815593</t>
+          <t>1817858</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1938963</t>
+          <t>1940239</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3719166</t>
+          <t>3713558</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3884909</t>
+          <t>3884577</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1036162</t>
+          <t>1038550</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1144236</t>
+          <t>1146310</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1120475</t>
+          <t>1115611</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1234693</t>
+          <t>1230053</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2196990</t>
+          <t>2191828</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2356714</t>
+          <t>2350871</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>257065</t>
+          <t>257204</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>324670</t>
+          <t>325954</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>330084</t>
+          <t>333875</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>404202</t>
+          <t>405536</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>607150</t>
+          <t>610938</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>705564</t>
+          <t>712813</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>33183</t>
+          <t>33197</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>61817</t>
+          <t>62022</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>63926</t>
+          <t>63603</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>100230</t>
+          <t>101291</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>106011</t>
+          <t>102115</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>150858</t>
+          <t>150874</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,7 +9121,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11586</t>
+          <t>11473</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>29458</t>
+          <t>28293</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15731</t>
+          <t>16290</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>34887</t>
+          <t>35960</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>30545</t>
+          <t>31897</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>58543</t>
+          <t>57444</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -9605,32 +9605,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>269076</t>
+          <t>298445</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>246782</t>
+          <t>274067</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>290026</t>
+          <t>319903</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9640,32 +9640,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>353434</t>
+          <t>373950</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>333304</t>
+          <t>352278</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>375213</t>
+          <t>395570</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9675,32 +9675,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>622510</t>
+          <t>672395</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>594138</t>
+          <t>639201</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>651909</t>
+          <t>707228</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>50,95%</t>
         </is>
       </c>
     </row>
@@ -9718,32 +9718,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>138739</t>
+          <t>153569</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>135189</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>158653</t>
+          <t>174822</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9753,32 +9753,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>223586</t>
+          <t>250006</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>205495</t>
+          <t>231300</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>243603</t>
+          <t>273641</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9788,32 +9788,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>362325</t>
+          <t>403576</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>334659</t>
+          <t>372661</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>387535</t>
+          <t>433635</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>31,24%</t>
         </is>
       </c>
     </row>
@@ -9831,32 +9831,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>53724</t>
+          <t>64380</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41439</t>
+          <t>51557</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>83763</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9866,32 +9866,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>93399</t>
+          <t>103211</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>78323</t>
+          <t>89887</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>105682</t>
+          <t>117603</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9901,32 +9901,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>147122</t>
+          <t>167591</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>130786</t>
+          <t>147303</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>166227</t>
+          <t>190935</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -9944,32 +9944,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37455</t>
+          <t>43094</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28859</t>
+          <t>32964</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48692</t>
+          <t>54957</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>55372</t>
+          <t>61367</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46181</t>
+          <t>50242</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66480</t>
+          <t>73221</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10014,32 +10014,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>92828</t>
+          <t>104461</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>78117</t>
+          <t>89718</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>107143</t>
+          <t>121031</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14193</t>
+          <t>17351</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9121</t>
+          <t>11551</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21633</t>
+          <t>26213</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>19395</t>
+          <t>22618</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13808</t>
+          <t>16025</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26471</t>
+          <t>30560</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>33588</t>
+          <t>39969</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25612</t>
+          <t>31227</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>42810</t>
+          <t>51637</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>513187</t>
+          <t>576839</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>513187</t>
+          <t>576839</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>513187</t>
+          <t>576839</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>745186</t>
+          <t>811153</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>745186</t>
+          <t>811153</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>745186</t>
+          <t>811153</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10240,17 +10240,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1258373</t>
+          <t>1387992</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1258373</t>
+          <t>1387992</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1258373</t>
+          <t>1387992</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10287,32 +10287,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1456707</t>
+          <t>1289855</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1334219</t>
+          <t>1236243</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1716580</t>
+          <t>1341991</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10322,32 +10322,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1192643</t>
+          <t>1212159</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>880999</t>
+          <t>1165666</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1337973</t>
+          <t>1252530</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10357,32 +10357,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2649350</t>
+          <t>2502015</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2282211</t>
+          <t>2431897</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2939218</t>
+          <t>2569965</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>58,55%</t>
         </is>
       </c>
     </row>
@@ -10400,32 +10400,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>605084</t>
+          <t>676331</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>415802</t>
+          <t>629283</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>698470</t>
+          <t>725902</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10435,32 +10435,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>625021</t>
+          <t>705661</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>456805</t>
+          <t>666790</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>711337</t>
+          <t>748435</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10470,32 +10470,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1230105</t>
+          <t>1381992</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>977867</t>
+          <t>1315773</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1373990</t>
+          <t>1443397</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>32,88%</t>
         </is>
       </c>
     </row>
@@ -10513,32 +10513,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>152456</t>
+          <t>177741</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>102924</t>
+          <t>152399</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>186482</t>
+          <t>207150</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10548,32 +10548,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>335191</t>
+          <t>150838</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>135665</t>
+          <t>131885</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>862872</t>
+          <t>172708</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10583,32 +10583,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>487647</t>
+          <t>328580</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>283439</t>
+          <t>294590</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1349675</t>
+          <t>364661</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -10626,32 +10626,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43241</t>
+          <t>49366</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29003</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59669</t>
+          <t>64211</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10661,32 +10661,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>61461</t>
+          <t>72471</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45112</t>
+          <t>57654</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77601</t>
+          <t>87258</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10696,32 +10696,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>104702</t>
+          <t>121837</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>80799</t>
+          <t>103245</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126614</t>
+          <t>142312</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>23720</t>
+          <t>28411</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14882</t>
+          <t>19386</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34948</t>
+          <t>39384</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>19864</t>
+          <t>26507</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12608</t>
+          <t>18721</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29450</t>
+          <t>38712</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>43584</t>
+          <t>54918</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30974</t>
+          <t>42554</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>57774</t>
+          <t>69331</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>0,97%</t>
         </is>
       </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -10852,17 +10852,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2281208</t>
+          <t>2221704</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2281208</t>
+          <t>2221704</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2281208</t>
+          <t>2221704</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10887,17 +10887,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2234180</t>
+          <t>2167637</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2234180</t>
+          <t>2167637</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2234180</t>
+          <t>2167637</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4515388</t>
+          <t>4389342</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4515388</t>
+          <t>4389342</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4515388</t>
+          <t>4389342</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10969,32 +10969,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>426422</t>
+          <t>472826</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>395841</t>
+          <t>444554</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>451481</t>
+          <t>498147</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11004,32 +11004,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>463620</t>
+          <t>509647</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>442836</t>
+          <t>486809</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>481103</t>
+          <t>531924</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11039,32 +11039,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>890041</t>
+          <t>982473</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>852063</t>
+          <t>948398</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>921060</t>
+          <t>1016830</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,59%</t>
         </is>
       </c>
     </row>
@@ -11082,32 +11082,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>163908</t>
+          <t>182615</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>142148</t>
+          <t>161535</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>189675</t>
+          <t>208076</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11117,32 +11117,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>157839</t>
+          <t>181195</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>140348</t>
+          <t>161073</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>177526</t>
+          <t>200615</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11152,32 +11152,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>321747</t>
+          <t>363810</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>293914</t>
+          <t>332251</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>351872</t>
+          <t>396779</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,55%</t>
         </is>
       </c>
     </row>
@@ -11195,32 +11195,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>39092</t>
+          <t>36111</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25495</t>
+          <t>25128</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>72534</t>
+          <t>51269</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11230,32 +11230,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19658</t>
+          <t>21690</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13211</t>
+          <t>15406</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28404</t>
+          <t>31727</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11265,32 +11265,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>58750</t>
+          <t>57802</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>44016</t>
+          <t>45354</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>96414</t>
+          <t>74297</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -11308,32 +11308,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9991</t>
+          <t>12783</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>6362</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19029</t>
+          <t>23928</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11343,32 +11343,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12437</t>
+          <t>14018</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7847</t>
+          <t>9216</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19022</t>
+          <t>21276</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11378,32 +11378,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>22428</t>
+          <t>26801</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15332</t>
+          <t>19094</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33094</t>
+          <t>39035</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3445</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -11431,22 +11431,22 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9118</t>
+          <t>10836</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11456,32 +11456,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4597</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2231</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>10970</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11491,22 +11491,22 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>9505</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15298</t>
+          <t>17173</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -11534,17 +11534,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>642859</t>
+          <t>707893</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>642859</t>
+          <t>707893</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>642859</t>
+          <t>707893</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11569,17 +11569,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>658151</t>
+          <t>732498</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>658151</t>
+          <t>732498</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>658151</t>
+          <t>732498</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11604,17 +11604,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1301009</t>
+          <t>1440391</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1301009</t>
+          <t>1440391</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1301009</t>
+          <t>1440391</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11651,32 +11651,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2152206</t>
+          <t>2061126</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2034129</t>
+          <t>1998034</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2460446</t>
+          <t>2123438</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11686,32 +11686,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2009697</t>
+          <t>2095756</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1685891</t>
+          <t>2039712</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2165836</t>
+          <t>2150653</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11721,32 +11721,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4161903</t>
+          <t>4156883</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3802753</t>
+          <t>4071100</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4437798</t>
+          <t>4230662</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>58,61%</t>
         </is>
       </c>
     </row>
@@ -11764,32 +11764,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>907731</t>
+          <t>1012516</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>694924</t>
+          <t>962315</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>995598</t>
+          <t>1077810</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1006446</t>
+          <t>1136862</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>823263</t>
+          <t>1083457</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1093033</t>
+          <t>1189060</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11834,32 +11834,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1914178</t>
+          <t>2149378</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1657947</t>
+          <t>2082056</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2059043</t>
+          <t>2226038</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>30,84%</t>
         </is>
       </c>
     </row>
@@ -11877,32 +11877,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>245272</t>
+          <t>278232</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>189828</t>
+          <t>247066</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>285156</t>
+          <t>319950</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11912,32 +11912,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>448247</t>
+          <t>275740</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>246995</t>
+          <t>246769</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>961276</t>
+          <t>300952</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11947,32 +11947,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>693519</t>
+          <t>553972</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>483559</t>
+          <t>509658</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1386250</t>
+          <t>594301</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -11990,32 +11990,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>90687</t>
+          <t>105243</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>71133</t>
+          <t>85777</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>111763</t>
+          <t>127436</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12025,32 +12025,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>129270</t>
+          <t>147855</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>105480</t>
+          <t>129409</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>150856</t>
+          <t>168733</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>219957</t>
+          <t>253099</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>184348</t>
+          <t>227382</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>248007</t>
+          <t>281890</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -12103,102 +12103,102 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>41358</t>
+          <t>49319</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>29791</t>
+          <t>38165</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>54712</t>
+          <t>64418</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>55074</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>43938</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>68079</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>104392</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>86944</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>123579</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>1,2%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>43856</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>34100</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>57116</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>85214</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>69946</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>103344</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3437254</t>
+          <t>3506436</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3437254</t>
+          <t>3506436</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3437254</t>
+          <t>3506436</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3637517</t>
+          <t>3711288</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3637517</t>
+          <t>3711288</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3637517</t>
+          <t>3711288</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7074771</t>
+          <t>7217725</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7074771</t>
+          <t>7217725</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7074771</t>
+          <t>7217725</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
